--- a/files/12-1429-havenhurst-dr.xlsx
+++ b/files/12-1429-havenhurst-dr.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8EE6DCD-C671-493E-A2EB-6B407AA90CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E941CAF5-BF9F-420C-8575-387FB7525433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3ACD6D5C-CACC-4472-B674-15395E7EE2EC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8B0F9D03-4FB9-49FC-A437-6CEFF116E1EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
     <sheet name="12 1429 Havenhurst Dr" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'12 1429 Havenhurst Dr'!$A$1:$N$78</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="142">
   <si>
     <t>LAAA UNDERWRITING BENCHMARKS (edit here; every deal tab reads these)</t>
   </si>
@@ -195,7 +192,10 @@
     <t>LoopNet listing</t>
   </si>
   <si>
-    <t>Data pulled 9/17/2026 from LoopNet public listing</t>
+    <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Marcus &amp; Millichap, Aug 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTE: | OM: Vacant unit: H03 (1 Bd / 1 Ba, 600 SF) shows 'Vacant' on the rent roll; counted here at the OM asking/market rent of $2,350 per the rules.; Two 'current' GSR figures in the OM: the Financial Summary / Operating Statement Gross Scheduled (Current) Rent is $359,102 (occupied units only, vacant H03 at  | OM: Vacant unit: H03 (1 Bd / 1 Ba, 600 SF) shows 'Vacant' on the rent roll; counted here at the OM asking/market rent of $2,350 per the rules.; Two 'current' GSR figures in the OM: the Financial Summary / Operating Statement Gross Scheduled (Current) Rent is $359,102 (occupied units only, vacant H03 at </t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -300,13 +300,13 @@
     <t>Rent source</t>
   </si>
   <si>
-    <t>1 Bd / 1 Ba  (~750 SF)</t>
-  </si>
-  <si>
-    <t>Allocated from published GRM (price / GRM) using LAAA bed weights</t>
-  </si>
-  <si>
-    <t>2 Bd / 2 Ba  (~1000 SF)</t>
+    <t>1 Bd / 1 Ba  (~609 SF)  [15 occupied at $628-$2,557 (sum $23,093/mo) plus unit H03 va]</t>
+  </si>
+  <si>
+    <t>OM rent roll, current in-place rents (OM Aug 2026)</t>
+  </si>
+  <si>
+    <t>2 Bd / 2 Ba  (~915 SF)  [H01 $3,681 and H21 $3,150; OM shows avg $3,415, $6,831/mo.]</t>
   </si>
   <si>
     <t>Total / weighted avg</t>
@@ -327,7 +327,7 @@
     <t>Scheduled gross rent</t>
   </si>
   <si>
-    <t>OM column: price / published GRM</t>
+    <t>OM column: OM stated current scheduled rent (OM Aug 2026); LAAA column: OM rent roll by unit type</t>
   </si>
   <si>
     <t>Other income (laundry, parking, RUBS)</t>
@@ -339,7 +339,7 @@
     <t>Vacancy &amp; credit loss</t>
   </si>
   <si>
-    <t>OM 3.0% (OM figure if extracted, else 3% assumed); LAAA per Assumptions</t>
+    <t>OM 3.0%; LAAA per Assumptions</t>
   </si>
   <si>
     <t>Effective gross income</t>
@@ -384,7 +384,7 @@
     <t>Utilities (water/sewer/trash/common electric &amp; gas)</t>
   </si>
   <si>
-    <t>per unit, by city</t>
+    <t>per unit, by city; OM utilities + water/sewer + gas/electric + trash combined</t>
   </si>
   <si>
     <t>Contract services (landscape, pest, cleaning)</t>
@@ -393,10 +393,10 @@
     <t>per unit</t>
   </si>
   <si>
-    <t>Admin / legal / licenses / rent registration</t>
-  </si>
-  <si>
-    <t>per unit; OM "other" items land here</t>
+    <t>Admin / legal / licenses / rent registration / other OM items</t>
+  </si>
+  <si>
+    <t>OM other items: General &amp; Administrative (gifts, appliances, bank charges, credit checks) 1,554</t>
   </si>
   <si>
     <t>Replacement reserves</t>
@@ -405,7 +405,7 @@
     <t>Total operating expenses</t>
   </si>
   <si>
-    <t>OM line items not published. OM total IMPLIED = OM EGI - (price x published cap)</t>
+    <t>OM line items from OM (OM Aug 2026); basis: OM 'Current' column (Financial Summary p.10 / Operating Statement p.12), identical to Year 1. Utilities, trash, G&amp;A and insurance read as owner actuals per OM notes; real estate taxes are pro forma at list price (OM footnote), not current; reserves are a broker assumption of $200/unit. No management fee and no repairs &amp; maintenance line anywhere in the OM. Electric $1,050 + gas $363 combined into gas_electric.; OM total 85,740</t>
   </si>
   <si>
     <t>Expenses per unit</t>
@@ -421,6 +421,9 @@
   </si>
   <si>
     <t>Net operating income</t>
+  </si>
+  <si>
+    <t>OM states NOI 267,991 / cap 5.58</t>
   </si>
   <si>
     <t>Cap rate on asking price</t>
@@ -469,12 +472,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="\$#,##0;\(\$#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,9 +523,24 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -559,7 +578,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -595,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -608,6 +628,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -615,16 +636,18 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,7 +680,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFC048CF-DDBD-464E-B44D-30B6E955459C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1D4B6D7-EDDC-41E2-A774-A6CBECF1E202}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -968,7 +991,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6266E144-98F6-432B-8EE0-8F9529C6BDA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1544547-DB19-4B46-9BD7-0321DAD69796}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1337,7 +1360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E70C38F7-DFF1-4A3D-B769-DA96DC47CF70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE098E0-8738-4135-AF2A-6B0ECCDC9A0E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1368,48 +1391,53 @@
         <v>50</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="A6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="14">
+        <v>53</v>
+      </c>
+      <c r="B7" s="15">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="14">
+        <v>54</v>
+      </c>
+      <c r="B8" s="15">
         <v>13824</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="14">
+        <v>55</v>
+      </c>
+      <c r="B9" s="15">
         <v>15246</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="15">
+        <v>56</v>
+      </c>
+      <c r="B10" s="16">
         <v>0.35</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11">
         <v>1949</v>
@@ -1417,39 +1445,39 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="8">
         <v>4287317</v>
@@ -1457,38 +1485,38 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
+      <c r="A21" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="4">
         <v>4800000</v>
@@ -1496,7 +1524,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" s="8">
         <f>IFERROR(B22/B7,"")</f>
@@ -1505,319 +1533,323 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="16">
+        <v>76</v>
+      </c>
+      <c r="B24" s="17">
         <f>IFERROR(B22/B8,"")</f>
         <v>347.22222222222223</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" s="17">
+        <v>77</v>
+      </c>
+      <c r="B25" s="18">
         <v>5.5599999999999997E-2</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="18">
+        <v>78</v>
+      </c>
+      <c r="B26" s="19">
         <v>13.6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
+      <c r="A28" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="19" t="s">
+      <c r="A29" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="B29" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="C29" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="D29" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="E29" s="20" t="s">
         <v>84</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" s="14">
+        <v>86</v>
+      </c>
+      <c r="B30" s="15">
         <v>16</v>
       </c>
-      <c r="C30" s="20">
-        <v>1573</v>
-      </c>
-      <c r="D30" s="8">
+      <c r="C30" s="21">
+        <v>1590</v>
+      </c>
+      <c r="D30" s="22">
         <f>B30*C30</f>
-        <v>25168</v>
-      </c>
-      <c r="E30" s="8">
+        <v>25440</v>
+      </c>
+      <c r="E30" s="22">
         <f>D30*12</f>
-        <v>302016</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>86</v>
+        <v>305280</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="15">
+        <v>2</v>
+      </c>
+      <c r="C31" s="21">
+        <v>3416</v>
+      </c>
+      <c r="D31" s="22">
+        <f>B31*C31</f>
+        <v>6832</v>
+      </c>
+      <c r="E31" s="22">
+        <f>D31*12</f>
+        <v>81984</v>
+      </c>
+      <c r="F31" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="14">
-        <v>2</v>
-      </c>
-      <c r="C31" s="20">
-        <v>2123</v>
-      </c>
-      <c r="D31" s="8">
-        <f>B31*C31</f>
-        <v>4246</v>
-      </c>
-      <c r="E31" s="8">
-        <f>D31*12</f>
-        <v>50952</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="22">
+      <c r="A32" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="25">
         <f>SUM(B30:B31)</f>
         <v>18</v>
       </c>
-      <c r="C32" s="23">
+      <c r="C32" s="26">
         <f>IFERROR(D32/B32,"")</f>
-        <v>1634.1111111111111</v>
-      </c>
-      <c r="D32" s="23">
+        <v>1792.8888888888889</v>
+      </c>
+      <c r="D32" s="26">
         <f>SUM(D30:D31)</f>
-        <v>29414</v>
-      </c>
-      <c r="E32" s="23">
+        <v>32272</v>
+      </c>
+      <c r="E32" s="26">
         <f>SUM(E30:E31)</f>
-        <v>352968</v>
+        <v>387264</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
+      <c r="A34" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" s="24" t="s">
+      <c r="A35" s="27"/>
+      <c r="B35" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24" t="s">
+      <c r="C35" s="27" t="s">
         <v>92</v>
+      </c>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="8">
-        <v>352941.17647058831</v>
+        <v>94</v>
+      </c>
+      <c r="B36" s="22">
+        <v>387302</v>
       </c>
       <c r="C36" s="8">
         <f>E32</f>
-        <v>352968</v>
+        <v>387264</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B37" s="8">
-        <v>0</v>
+        <v>5402</v>
       </c>
       <c r="C37" s="4">
-        <v>0</v>
+        <v>5402</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
-        <v>96</v>
+      <c r="A38" s="24" t="s">
+        <v>97</v>
       </c>
       <c r="B38" s="8">
         <f>B36+B37</f>
-        <v>352941.17647058831</v>
+        <v>392704</v>
       </c>
       <c r="C38" s="8">
         <f>C36+C37</f>
-        <v>352968</v>
+        <v>392666</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B39" s="8">
         <f>-B36*0.03</f>
-        <v>-10588.235294117649</v>
+        <v>-11619.06</v>
       </c>
       <c r="C39" s="8">
         <f>-C36*Assumptions!$B$3</f>
-        <v>-10589.039999999999</v>
+        <v>-11617.92</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="B40" s="23">
+      <c r="A40" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="26">
         <f>B38+B39</f>
-        <v>342352.94117647066</v>
-      </c>
-      <c r="C40" s="23">
+        <v>381084.94</v>
+      </c>
+      <c r="C40" s="26">
         <f>C38+C39</f>
-        <v>342378.96</v>
+        <v>381048.08</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
+      <c r="A42" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="24" t="s">
+      <c r="A43" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="B43" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="24" t="s">
+      <c r="C43" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="F43" s="24" t="s">
+      <c r="D43" s="27" t="s">
         <v>92</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F43" s="27" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="8"/>
+        <v>105</v>
+      </c>
+      <c r="B44" s="22">
+        <v>53760</v>
+      </c>
       <c r="C44" s="8">
         <f>B22*Assumptions!$B$18</f>
         <v>57600</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="28">
         <f>C44</f>
         <v>57600</v>
       </c>
-      <c r="E44" s="8" t="str">
+      <c r="E44" s="8">
         <f t="shared" ref="E44:E52" si="0">IF(ISNUMBER(B44),D44-B44,"")</f>
-        <v/>
+        <v>3840</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>106</v>
-      </c>
-      <c r="B45" s="8"/>
+        <v>107</v>
+      </c>
+      <c r="B45" s="22">
+        <v>15466</v>
+      </c>
       <c r="C45" s="8">
         <f>B7*Assumptions!$B$5+B8*Assumptions!$B$6</f>
         <v>17424</v>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="28">
         <f t="shared" ref="D45:D51" si="1">IF(ISNUMBER(B45),MAX(B45,C45),C45)</f>
         <v>17424</v>
       </c>
-      <c r="E45" s="8" t="str">
+      <c r="E45" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1958</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" s="8"/>
+        <v>109</v>
+      </c>
+      <c r="B46" s="22"/>
       <c r="C46" s="8">
         <f>C40*Assumptions!$B$4</f>
-        <v>17118.948</v>
-      </c>
-      <c r="D46" s="25">
+        <v>19052.404000000002</v>
+      </c>
+      <c r="D46" s="28">
         <f t="shared" si="1"/>
-        <v>17118.948</v>
+        <v>19052.404000000002</v>
       </c>
       <c r="E46" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F46" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>110</v>
-      </c>
-      <c r="B47" s="8"/>
+        <v>111</v>
+      </c>
+      <c r="B47" s="22"/>
       <c r="C47" s="8">
         <f>B7*Assumptions!$B$7</f>
         <v>21600</v>
       </c>
-      <c r="D47" s="25">
+      <c r="D47" s="28">
         <f t="shared" si="1"/>
         <v>21600</v>
       </c>
@@ -1826,40 +1858,42 @@
         <v/>
       </c>
       <c r="F47" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>112</v>
-      </c>
-      <c r="B48" s="8"/>
+        <v>113</v>
+      </c>
+      <c r="B48" s="22">
+        <v>11361</v>
+      </c>
       <c r="C48" s="8">
         <f>B7*Assumptions!$B$11</f>
         <v>28800</v>
       </c>
-      <c r="D48" s="25">
+      <c r="D48" s="28">
         <f t="shared" si="1"/>
         <v>28800</v>
       </c>
-      <c r="E48" s="8" t="str">
+      <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>17439</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>114</v>
-      </c>
-      <c r="B49" s="8"/>
+        <v>115</v>
+      </c>
+      <c r="B49" s="22"/>
       <c r="C49" s="8">
         <f>B7*Assumptions!$B$12</f>
         <v>7200</v>
       </c>
-      <c r="D49" s="25">
+      <c r="D49" s="28">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
@@ -1868,210 +1902,217 @@
         <v/>
       </c>
       <c r="F49" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>116</v>
-      </c>
-      <c r="B50" s="8"/>
+        <v>117</v>
+      </c>
+      <c r="B50" s="22">
+        <v>1554</v>
+      </c>
       <c r="C50" s="8">
         <f>B7*Assumptions!$B$13</f>
         <v>4500</v>
       </c>
-      <c r="D50" s="25">
+      <c r="D50" s="28">
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
-      <c r="E50" s="8" t="str">
+      <c r="E50" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2946</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>118</v>
-      </c>
-      <c r="B51" s="8"/>
+        <v>119</v>
+      </c>
+      <c r="B51" s="22">
+        <v>3600</v>
+      </c>
       <c r="C51" s="8">
         <f>B7*Assumptions!$B$14</f>
         <v>5400</v>
       </c>
-      <c r="D51" s="25">
+      <c r="D51" s="28">
         <f t="shared" si="1"/>
         <v>5400</v>
       </c>
-      <c r="E51" s="8" t="str">
+      <c r="E51" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B52" s="23">
-        <f>B40-B22*B25</f>
-        <v>75472.94117647066</v>
-      </c>
-      <c r="C52" s="23">
+      <c r="A52" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="26">
+        <f>SUM(B44:B51)</f>
+        <v>85741</v>
+      </c>
+      <c r="C52" s="26">
         <f>SUM(C44:C51)</f>
-        <v>159642.948</v>
-      </c>
-      <c r="D52" s="23">
+        <v>161576.40400000001</v>
+      </c>
+      <c r="D52" s="26">
         <f>SUM(D44:D51)</f>
-        <v>159642.948</v>
-      </c>
-      <c r="E52" s="23">
+        <v>161576.40400000001</v>
+      </c>
+      <c r="E52" s="26">
         <f t="shared" si="0"/>
-        <v>84170.006823529344</v>
+        <v>75835.40400000001</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B53" s="8">
         <f>IFERROR(B52/B7,"")</f>
-        <v>4192.9411764705919</v>
+        <v>4763.3888888888887</v>
       </c>
       <c r="C53" s="8">
         <f>IFERROR(C52/B7,"")</f>
-        <v>8869.0526666666665</v>
+        <v>8976.46688888889</v>
       </c>
       <c r="D53" s="8">
         <f>IFERROR(D52/B7,"")</f>
-        <v>8869.0526666666665</v>
+        <v>8976.46688888889</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>122</v>
-      </c>
-      <c r="B54" s="17">
+        <v>123</v>
+      </c>
+      <c r="B54" s="18">
         <f>IFERROR(B52/B40,"")</f>
-        <v>0.22045360824742286</v>
-      </c>
-      <c r="C54" s="17">
+        <v>0.22499183515360119</v>
+      </c>
+      <c r="C54" s="18">
         <f>IFERROR(C52/C40,"")</f>
-        <v>0.46627557955079946</v>
-      </c>
-      <c r="D54" s="17">
+        <v>0.42403153953695294</v>
+      </c>
+      <c r="D54" s="18">
         <f>IF(C36&gt;0,IFERROR(D52/C40,""),"")</f>
-        <v>0.46627557955079946</v>
+        <v>0.42403153953695294</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B55" s="26" t="str">
+      <c r="A55" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="29" t="str">
         <f>IF(ISNUMBER(B52),IF(D52&gt;B52*(1+Assumptions!$B$24),"OM EXPENSES LIGHT","OM expenses reasonable"),"OM expenses not published")</f>
         <v>OM EXPENSES LIGHT</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
+      <c r="A57" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="24"/>
-      <c r="B58" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" s="24" t="s">
+      <c r="A58" s="27"/>
+      <c r="B58" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24" t="s">
+      <c r="C58" s="27" t="s">
         <v>92</v>
       </c>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B59" s="23">
+      <c r="A59" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="26">
         <f>B40-B52</f>
-        <v>266880</v>
-      </c>
-      <c r="C59" s="23">
+        <v>295343.94</v>
+      </c>
+      <c r="C59" s="26">
         <f>IF(C36&gt;0,C40-D52,"")</f>
-        <v>182736.01200000002</v>
+        <v>219471.67600000001</v>
+      </c>
+      <c r="F59" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B60" s="17">
+      <c r="A60" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" s="18">
         <f>IFERROR(B59/B22,"")</f>
-        <v>5.5599999999999997E-2</v>
-      </c>
-      <c r="C60" s="17">
+        <v>6.1529987500000001E-2</v>
+      </c>
+      <c r="C60" s="18">
         <f>IF(C59="","",IFERROR(C59/B22,""))</f>
-        <v>3.8070002500000005E-2</v>
+        <v>4.5723265833333332E-2</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>128</v>
-      </c>
-      <c r="B61" s="18">
+        <v>130</v>
+      </c>
+      <c r="B61" s="19">
         <f>IFERROR(B22/B36,"")</f>
-        <v>13.599999999999998</v>
-      </c>
-      <c r="C61" s="18">
+        <v>12.393429416837506</v>
+      </c>
+      <c r="C61" s="19">
         <f>IF(C36&gt;0,IFERROR(B22/C36,""),"")</f>
-        <v>13.598966478547631</v>
+        <v>12.394645513138324</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B62" s="8">
         <f>IFERROR(B59/B7,"")</f>
-        <v>14826.666666666666</v>
+        <v>16407.996666666666</v>
       </c>
       <c r="C62" s="8">
         <f>IF(C59="","",IFERROR(C59/B7,""))</f>
-        <v>10152.000666666667</v>
+        <v>12192.870888888889</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
+      <c r="A64" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B65" s="8">
         <f>IFERROR(B22*Assumptions!$B$20,"")</f>
@@ -2080,79 +2121,78 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B66" s="8">
         <f>IF(C59="","",IFERROR(PV(Assumptions!$B$22/12,Assumptions!$B$23*12,-C59/Assumptions!$B$21/12),""))</f>
-        <v>1978570.8100347861</v>
+        <v>2376325.5365505735</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="21" t="s">
-        <v>133</v>
+      <c r="A67" s="24" t="s">
+        <v>135</v>
       </c>
       <c r="B67" s="8">
         <f>IFERROR(MIN(B65,B66),"")</f>
-        <v>1978570.8100347861</v>
+        <v>2376325.5365505735</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B68" s="8">
         <f>IFERROR(B22-B67,"")</f>
-        <v>2821429.1899652136</v>
+        <v>2423674.4634494265</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B69" s="8">
         <f>IFERROR(-PMT(Assumptions!$B$22/12,Assumptions!$B$23*12,B67)*12,"")</f>
-        <v>146188.80959999957</v>
+        <v>175577.34079999942</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>136</v>
-      </c>
-      <c r="B70" s="18">
+        <v>138</v>
+      </c>
+      <c r="B70" s="19">
         <f>IFERROR(C59/B69,"")</f>
-        <v>1.2500000000000038</v>
+        <v>1.2500000000000042</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B71" s="8">
         <f>IFERROR(C59-B69,"")</f>
-        <v>36547.202400000446</v>
+        <v>43894.335200000583</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>138</v>
-      </c>
-      <c r="B72" s="17">
+        <v>140</v>
+      </c>
+      <c r="B72" s="18">
         <f>IFERROR(B71/B68,"")</f>
-        <v>1.2953435985558457E-2</v>
+        <v>1.8110656303870615E-2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{9FF8E8A7-FEB6-4C17-9009-B8B5194411C1}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{C4A6BDF4-231F-446B-8606-5ACF7C73FECC}"/>
   </hyperlinks>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
-  <pageSetup scale="50" orientation="landscape" r:id="rId2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/files/12-1429-havenhurst-dr.xlsx
+++ b/files/12-1429-havenhurst-dr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E941CAF5-BF9F-420C-8575-387FB7525433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2FA4601-ECA9-4BF6-A516-2A463F56ACD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8B0F9D03-4FB9-49FC-A437-6CEFF116E1EB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2D497873-7460-41F2-A733-14959FB9D813}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Marcus &amp; Millichap, Aug 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">NOTE: | OM: Vacant unit: H03 (1 Bd / 1 Ba, 600 SF) shows 'Vacant' on the rent roll; counted here at the OM asking/market rent of $2,350 per the rules.; Two 'current' GSR figures in the OM: the Financial Summary / Operating Statement Gross Scheduled (Current) Rent is $359,102 (occupied units only, vacant H03 at  | OM: Vacant unit: H03 (1 Bd / 1 Ba, 600 SF) shows 'Vacant' on the rent roll; counted here at the OM asking/market rent of $2,350 per the rules.; Two 'current' GSR figures in the OM: the Financial Summary / Operating Statement Gross Scheduled (Current) Rent is $359,102 (occupied units only, vacant H03 at </t>
+    <t xml:space="preserve">NOTE: | OM: Vacant unit: H03 (1 Bd / 1 Ba, 600 SF) shows 'Vacant' on the rent roll; counted here at the OM asking/market rent of $2,350 per the rules.; Two 'current' GSR figures in the OM: the Financial Summary / Operating Statement Gross Scheduled (Current) Rent is $359,102 (occupied units only, vacant H03 at </t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -680,7 +680,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1D4B6D7-EDDC-41E2-A774-A6CBECF1E202}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33A9CCFF-DD70-4267-A02C-6E85A14700BF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -991,7 +991,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1544547-DB19-4B46-9BD7-0321DAD69796}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78AEF23A-6444-42BD-90CE-D1863CB24586}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1360,7 +1360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE098E0-8738-4135-AF2A-6B0ECCDC9A0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002A4B03-E0CE-4842-90AF-746967737D2C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2189,7 +2189,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{C4A6BDF4-231F-446B-8606-5ACF7C73FECC}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{E2CF0013-FF54-44D5-AF20-5D9F07DA26B6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId2"/>
